--- a/product_surveys/013_product_category_expansion_registration_form--product_surveys.xlsx
+++ b/product_surveys/013_product_category_expansion_registration_form--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_1</t>
+          <t>category_expansion_registration_form_page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Product Category Expansion Details</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_2</t>
+          <t>product_category_expansion_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Team Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_3</t>
+          <t>product_description_registration_form_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Product Description</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,58 +589,58 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_4</t>
+          <t>product_registration_form_page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Product Details</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_5</t>
+          <t>status_registration_form_page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Review Status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_6</t>
+          <t>product_status_details</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Status</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_7</t>
+          <t>review_registration_form_page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Reviewer Details</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,40 +676,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_8</t>
+          <t>review_status_registration_form_page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Review Status Registration Form Page 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_9</t>
+          <t>reviewer_details</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Reviewer Information</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_10</t>
+          <t>review_status</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Review Status (3)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_11</t>
+          <t>review_details</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reviewer</t>
+          <t>Review Details</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_12</t>
+          <t>reviewers_info</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Reviewer</t>
+          <t>Reviewers Info</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_13</t>
+          <t>review_status_registration_form_page_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reviewer</t>
+          <t>Review Status Registration Form Page 13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_14</t>
+          <t>review_details_registration_form_page_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Reviewer</t>
+          <t>Review Details Registration Form Page 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -873,170 +873,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_1_choices</t>
+          <t>category_expansion_registration_form_page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_1_choices</t>
+          <t>category_expansion_registration_form_page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_6_choices</t>
+          <t>status_registration_form_page_5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_6_choices</t>
+          <t>status_registration_form_page_5_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_7_choices</t>
+          <t>review_status_registration_form_page_8_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_7_choices</t>
+          <t>review_status_registration_form_page_8_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_9_choices</t>
+          <t>review_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_9_choices</t>
+          <t>review_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_13_choices</t>
+          <t>review_status_registration_form_page_13_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>product_category_expansion_registration_form_13_choices</t>
+          <t>review_status_registration_form_page_13_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
